--- a/app/templates/Seguimiento.xlsx
+++ b/app/templates/Seguimiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7562D0C3-7D55-43E4-B349-C87D2CC3FAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20FA36A-3CB2-4DBE-9794-6109E94DCD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="612" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
